--- a/artfynd/A 39425-2023 artfynd.xlsx
+++ b/artfynd/A 39425-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39425-2023 artfynd.xlsx
+++ b/artfynd/A 39425-2023 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>112680491</v>
       </c>
       <c r="B2" t="n">
-        <v>89298</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -794,62 +789,56 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112680504</v>
+        <v>113870271</v>
       </c>
       <c r="B3" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mattsarve, Gtl</t>
+          <t>Gammelgarn Mattsarve, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>728130</v>
+        <v>728123</v>
       </c>
       <c r="R3" t="n">
-        <v>6370653</v>
+        <v>6370581</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,35 +883,25 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Ängsgranskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113870279</v>
+        <v>113870165</v>
       </c>
       <c r="B4" t="n">
-        <v>86180</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>728123</v>
+        <v>728068</v>
       </c>
       <c r="R4" t="n">
-        <v>6370581</v>
+        <v>6370646</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,15 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113870197</v>
+        <v>113870279</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1079,13 +1053,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>728071</v>
+        <v>728123</v>
       </c>
       <c r="R5" t="n">
-        <v>6370640</v>
+        <v>6370581</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,15 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113870165</v>
+        <v>113870302</v>
       </c>
       <c r="B6" t="n">
-        <v>86180</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>728068</v>
+        <v>728153</v>
       </c>
       <c r="R6" t="n">
-        <v>6370646</v>
+        <v>6370558</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113870271</v>
+        <v>113870197</v>
       </c>
       <c r="B7" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,26 +1236,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1307,13 +1271,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>728123</v>
+        <v>728071</v>
       </c>
       <c r="R7" t="n">
-        <v>6370581</v>
+        <v>6370640</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1370,37 +1334,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113870302</v>
+        <v>112680504</v>
       </c>
       <c r="B8" t="n">
-        <v>86180</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1410,21 +1369,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelgarn Mattsarve, Gtl</t>
+          <t>Mattsarve, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>728153</v>
+        <v>728130</v>
       </c>
       <c r="R8" t="n">
-        <v>6370558</v>
+        <v>6370652</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,12 +1411,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,15 +1429,20 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 39425-2023 artfynd.xlsx
+++ b/artfynd/A 39425-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112680491</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113870271</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113870165</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113870279</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113870302</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113870197</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,8 +1481,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112680504</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>